--- a/analyses/data/nonpara_anova_time.xlsx
+++ b/analyses/data/nonpara_anova_time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexikeene/Documents/Research/diverse_collections/github/analyses/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E33F44D7-9CC1-B441-A1E6-A94E5439F66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61130DCF-7931-E24D-A34B-ED9751D44E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34480" yWindow="980" windowWidth="27640" windowHeight="16700" xr2:uid="{E28376A0-E532-4145-9A06-9A5AB67BAEC9}"/>
+    <workbookView xWindow="40940" yWindow="720" windowWidth="27640" windowHeight="16700" xr2:uid="{E28376A0-E532-4145-9A06-9A5AB67BAEC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>Comparison</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Wabash</t>
+  </si>
+  <si>
+    <t>(1) Bonferroni adjusted P value  for multiple hypothesis testing</t>
   </si>
 </sst>
 </file>
@@ -126,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -149,49 +152,14 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Lucida Grande"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Lucida Grande"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -290,6 +258,44 @@
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Lucida Grande"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Lucida Grande"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -304,8 +310,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EF8C0B0-4BC7-C245-B739-92EBFECB5BCB}" name="Table1" displayName="Table1" ref="A1:E7" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:E7" xr:uid="{9EF8C0B0-4BC7-C245-B739-92EBFECB5BCB}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EF8C0B0-4BC7-C245-B739-92EBFECB5BCB}" name="Table1" displayName="Table1" ref="A1:E8" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E8" xr:uid="{9EF8C0B0-4BC7-C245-B739-92EBFECB5BCB}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -313,11 +319,11 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{56467076-4D2C-CA41-A889-D727B6B593DB}" name="Location" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{194CE23B-8B98-494E-9083-E26062F6A7F9}" name="Comparison" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{146140BC-67A0-3048-B426-A58A9180AA08}" name="Z" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{F5872FFA-CBB3-4344-9C9F-0ED4BD94887C}" name="P.unadj" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{15D00C78-732B-5840-A765-8F18B3D5B905}" name="P.adj" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{56467076-4D2C-CA41-A889-D727B6B593DB}" name="Location" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{194CE23B-8B98-494E-9083-E26062F6A7F9}" name="Comparison" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{146140BC-67A0-3048-B426-A58A9180AA08}" name="Z" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{F5872FFA-CBB3-4344-9C9F-0ED4BD94887C}" name="P.unadj" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{15D00C78-732B-5840-A765-8F18B3D5B905}" name="P.adj" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -640,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{578D0F4F-BCFF-E849-A7E6-9E0C582AE259}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -766,6 +772,15 @@
         <v>2.7523400000000001E-7</v>
       </c>
     </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
